--- a/02_Metadata/ANAC/Indicators_ANAC.xlsx
+++ b/02_Metadata/ANAC/Indicators_ANAC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gaiascarponi/Desktop/MIPA/Monitoraggio-PNRR/02_Metadata/ANAC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9DE696-6111-5D44-9D97-E26C435B8092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F27A36C7-EF2E-9245-8759-7BF4273636F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17080" yWindow="700" windowWidth="17120" windowHeight="21460" xr2:uid="{13670AD8-CA4D-E544-80D8-0DFF87BDA3B0}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" xr2:uid="{13670AD8-CA4D-E544-80D8-0DFF87BDA3B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="76">
   <si>
     <t xml:space="preserve">Dataset </t>
   </si>
@@ -101,27 +101,12 @@
     <t>Cf_amministrazione_appaltante</t>
   </si>
   <si>
-    <t>CIG_2024</t>
-  </si>
-  <si>
-    <t>CIG_2025</t>
-  </si>
-  <si>
-    <t>CIG_2026</t>
-  </si>
-  <si>
     <t>Numero totale di PA matchate</t>
   </si>
   <si>
     <t>Percentuale di PA matchate rispetto al totale della lista MPA</t>
   </si>
   <si>
-    <t>Numero di gare per ogni PA</t>
-  </si>
-  <si>
-    <t>Somma degli importi per ogni PA</t>
-  </si>
-  <si>
     <t>(Sum(unique(X1))/sum(unique(X2))*100</t>
   </si>
   <si>
@@ -135,6 +120,153 @@
   </si>
   <si>
     <t xml:space="preserve">sum(X1) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numero totale di Gare </t>
+  </si>
+  <si>
+    <t>ind5</t>
+  </si>
+  <si>
+    <t>mean(X1)</t>
+  </si>
+  <si>
+    <t>DURATA_PREVISTA</t>
+  </si>
+  <si>
+    <t>mean(X1-X2)</t>
+  </si>
+  <si>
+    <t>data_scadenza_offerta</t>
+  </si>
+  <si>
+    <t>DATA_COMUNICAZIONE_ESITO</t>
+  </si>
+  <si>
+    <t>ind6</t>
+  </si>
+  <si>
+    <t>ind7</t>
+  </si>
+  <si>
+    <t>Media GLOBALE finestra per partecipare</t>
+  </si>
+  <si>
+    <t>ind8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Media GLOBALE numero di gare </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Media GLOBALE importo lotto </t>
+  </si>
+  <si>
+    <t>Media GLOBALE durata prevista</t>
+  </si>
+  <si>
+    <t>ind9</t>
+  </si>
+  <si>
+    <t>Numero gare per PA</t>
+  </si>
+  <si>
+    <t>fil_anno</t>
+  </si>
+  <si>
+    <t>data_pubblicazione</t>
+  </si>
+  <si>
+    <t>ind10</t>
+  </si>
+  <si>
+    <t>Importo lotto per PA</t>
+  </si>
+  <si>
+    <t>ind11</t>
+  </si>
+  <si>
+    <t>Numero totale di Gare Aggiudicate</t>
+  </si>
+  <si>
+    <t>ind12</t>
+  </si>
+  <si>
+    <t>ind13</t>
+  </si>
+  <si>
+    <t>Media GLOBALE durata effettiva</t>
+  </si>
+  <si>
+    <t>ind14</t>
+  </si>
+  <si>
+    <t>Numero gare aggiudicate per PA</t>
+  </si>
+  <si>
+    <t>Percentuale gare aggiudicate per PA</t>
+  </si>
+  <si>
+    <t>ind15</t>
+  </si>
+  <si>
+    <t>Media GLOBALE numero di gare aggiudicate</t>
+  </si>
+  <si>
+    <t>ind16</t>
+  </si>
+  <si>
+    <t>ind17</t>
+  </si>
+  <si>
+    <t>ind18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Media PONDERATA importo lotto per PA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Media PONDERATA durata prevista per PA </t>
+  </si>
+  <si>
+    <t>Media PONDERATA durata effettiva per PA</t>
+  </si>
+  <si>
+    <t>Media PONDERATA finestra per partecipare per PA</t>
+  </si>
+  <si>
+    <t>ESITO=="AGGIUDICATA"</t>
+  </si>
+  <si>
+    <t>X1/X2*100</t>
+  </si>
+  <si>
+    <t>X1/X2</t>
+  </si>
+  <si>
+    <t>ind19</t>
+  </si>
+  <si>
+    <t>ind20</t>
+  </si>
+  <si>
+    <t>ind21</t>
+  </si>
+  <si>
+    <t>ind22</t>
+  </si>
+  <si>
+    <t>ind23</t>
+  </si>
+  <si>
+    <t>ind24</t>
+  </si>
+  <si>
+    <t>ind25</t>
+  </si>
+  <si>
+    <t>ind26</t>
+  </si>
+  <si>
+    <t>fil_mese</t>
   </si>
 </sst>
 </file>
@@ -520,16 +652,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309BF556-1530-FF4C-AF18-30E50F70D174}">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.1640625" customWidth="1"/>
+    <col min="4" max="4" width="50.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.6640625" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.5" bestFit="1" customWidth="1"/>
@@ -584,7 +716,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
       </c>
       <c r="G2" t="s">
         <v>18</v>
@@ -601,22 +736,28 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>28</v>
+        <v>23</v>
+      </c>
+      <c r="K3">
+        <v>2026</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -624,19 +765,25 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>43</v>
       </c>
       <c r="G4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>29</v>
+        <v>24</v>
+      </c>
+      <c r="K4">
+        <v>2026</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -644,109 +791,651 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
       </c>
       <c r="D5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" t="s">
         <v>26</v>
       </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>64</v>
+      </c>
+      <c r="K5">
+        <v>2026</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>2026</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7">
+        <v>2026</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8">
+        <v>2026</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10">
+        <v>2026</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" t="s">
+        <v>4</v>
+      </c>
+      <c r="I11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>2026</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>16</v>
       </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12">
+        <v>2026</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13">
+        <v>2026</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K14">
+        <v>2026</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>16</v>
       </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" t="s">
+        <v>30</v>
+      </c>
+      <c r="K15">
+        <v>2026</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" t="s">
+        <v>64</v>
+      </c>
+      <c r="K16">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" t="s">
+        <v>33</v>
+      </c>
+      <c r="I18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" t="s">
+        <v>44</v>
+      </c>
+      <c r="K19">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22" t="s">
+        <v>25</v>
+      </c>
+      <c r="K22">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>16</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" t="s">
+        <v>75</v>
+      </c>
+      <c r="G23" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" t="s">
+        <v>64</v>
+      </c>
+      <c r="K24">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" t="s">
+        <v>65</v>
+      </c>
+      <c r="H25" t="s">
+        <v>52</v>
+      </c>
+      <c r="I25" t="s">
+        <v>45</v>
+      </c>
+      <c r="K25">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" t="s">
+        <v>75</v>
+      </c>
+      <c r="G26" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" t="s">
+        <v>33</v>
+      </c>
+      <c r="I26" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" t="s">
+        <v>44</v>
+      </c>
+      <c r="K27">
+        <v>2026</v>
       </c>
     </row>
   </sheetData>
